--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -50664,47 +50664,47 @@
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>17125360</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Avenida PERPETUO SOCORRO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:35</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I41" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:57</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J41" s="29" t="n">
@@ -50714,47 +50714,47 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17125360</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>439 - BOSQUE CARANDÁ</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>25/08/2026 09:35</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>25/08/2026 09:57</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -51314,7 +51314,7 @@
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -51324,37 +51324,37 @@
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17098947</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>75 - R</t>
         </is>
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>24/08/2026 09:26</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>24/08/2026 09:46</t>
         </is>
       </c>
       <c r="J54" s="29" t="n">
@@ -51364,47 +51364,47 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17112709</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>295 - 1 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>24/08/2026 15:00</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>24/08/2026 15:20</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -51414,7 +51414,7 @@
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
@@ -51424,37 +51424,37 @@
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>17098947</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>75 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:26</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:46</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J56" s="29" t="n">
@@ -51614,47 +51614,47 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>17112709</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:00</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:20</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J60" s="29" t="n">
@@ -52114,47 +52114,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -52224,7 +52224,7 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
@@ -52239,22 +52239,22 @@
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -52324,7 +52324,7 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
@@ -52339,22 +52339,22 @@
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J74" s="29" t="n">
@@ -52374,7 +52374,7 @@
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
@@ -52384,27 +52384,27 @@
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I75" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J75" s="29" t="n">
@@ -52814,47 +52814,47 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -52914,7 +52914,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -52924,37 +52924,37 @@
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -53064,7 +53064,7 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
@@ -53074,37 +53074,37 @@
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -53274,7 +53274,7 @@
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
@@ -53284,27 +53284,27 @@
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -55464,7 +55464,7 @@
     <row r="137">
       <c r="A137" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B137" s="29" t="inlineStr">
@@ -55474,37 +55474,37 @@
       </c>
       <c r="C137" s="30" t="inlineStr">
         <is>
-          <t>17098957</t>
+          <t>17178582</t>
         </is>
       </c>
       <c r="D137" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E137" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="F137" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua ROSA AMARELA</t>
         </is>
       </c>
       <c r="G137" s="29" t="inlineStr">
         <is>
-          <t>258 - R</t>
+          <t>305 - R</t>
         </is>
       </c>
       <c r="H137" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:31</t>
+          <t>27/08/2026 09:33</t>
         </is>
       </c>
       <c r="I137" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>27/08/2026 09:49</t>
         </is>
       </c>
       <c r="J137" s="29" t="n">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="C138" s="30" t="inlineStr">
         <is>
-          <t>17098959</t>
+          <t>17098957</t>
         </is>
       </c>
       <c r="D138" s="29" t="inlineStr">
@@ -55544,17 +55544,17 @@
       </c>
       <c r="G138" s="29" t="inlineStr">
         <is>
-          <t>332 - R</t>
+          <t>258 - R</t>
         </is>
       </c>
       <c r="H138" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:05</t>
+          <t>24/08/2026 14:31</t>
         </is>
       </c>
       <c r="I138" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:21</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="J138" s="29" t="n">
@@ -55564,7 +55564,7 @@
     <row r="139">
       <c r="A139" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B139" s="29" t="inlineStr">
@@ -55574,37 +55574,37 @@
       </c>
       <c r="C139" s="30" t="inlineStr">
         <is>
-          <t>17178582</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D139" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E139" s="29" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F139" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AMARELA</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G139" s="29" t="inlineStr">
         <is>
-          <t>305 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H139" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 09:33</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I139" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 09:49</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J139" s="29" t="n">
@@ -55624,7 +55624,7 @@
       </c>
       <c r="C140" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17098959</t>
         </is>
       </c>
       <c r="D140" s="29" t="inlineStr">
@@ -55644,17 +55644,17 @@
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>332 - R</t>
         </is>
       </c>
       <c r="H140" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>24/08/2026 15:05</t>
         </is>
       </c>
       <c r="I140" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>24/08/2026 15:21</t>
         </is>
       </c>
       <c r="J140" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C20" s="41" t="inlineStr">
